--- a/www/download/COUNTRY.LUX.rpO2.xlsx
+++ b/www/download/COUNTRY.LUX.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.729948331892089</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.767200655768488</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.885559175181254</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.898529053504176</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.93826237298063</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.08271974788869</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.11656987032739</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1.0575296608032</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.88401700995807</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803923167763008</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803793921900143</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.796431998962022</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729660741064353</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.6799020733193</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.71694868579003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>-0.778274585994483</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>-0.850948000229026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>-0.830396865684383</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>-0.858119369317948</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.897759332708162</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>-0.935302532950754</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>-0.937787141281457</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>-0.929247760661226</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>-0.932153653005367</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>-0.932804632631777</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>-0.944906457650844</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>-0.945152117535535</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>-0.933439008803355</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-0.926904285065601</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.916582272950665</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>-0.772100268719556</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>-0.847580385425714</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>-0.826641402709035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>-0.839686507075086</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>-0.873524929019119</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>-0.912208636224834</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>-0.915318846053886</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>-0.90335912176085</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>-0.912224201342145</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>-0.909047092151476</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>-0.926037759150812</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>-0.92554758769939</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>-0.910408928151051</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>-0.900640509116042</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>-0.882805089913284</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>347.657</t>
+          <t>-0.743433549944837</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>356.525</t>
+          <t>-0.828482898327694</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>369.458</t>
+          <t>-0.804741465827506</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>384.402</t>
+          <t>-0.813828189817248</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>405.671</t>
+          <t>-0.847934377986587</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>430.518</t>
+          <t>-0.889771548266479</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>450.569</t>
+          <t>-0.893208472997709</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>464.123</t>
+          <t>-0.879078672160822</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>472.77</t>
+          <t>-0.920457486387393</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>488.325</t>
+          <t>-0.889646754736398</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>502.605</t>
+          <t>-0.91147336283669</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>520.128</t>
+          <t>-0.911764951437599</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>542.963</t>
+          <t>-0.893295087965072</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>608.296</t>
+          <t>-0.880906147950531</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>598.729</t>
+          <t>-0.855085121012677</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>314.909</t>
+          <t>13052484970.0113</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>322.522</t>
+          <t>9603686599.42789</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>334.262</t>
+          <t>8513632587.59741</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>348.888</t>
+          <t>9771913156.44311</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>370.292</t>
+          <t>11455323657.1459</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>393.85</t>
+          <t>15078684526.9368</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>414.011</t>
+          <t>14565375858.9595</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>426.888</t>
+          <t>12802281378.2777</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>435.429</t>
+          <t>16693419876.996</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>451.042</t>
+          <t>18564088828.0943</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>465.533</t>
+          <t>21483836568.6976</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>483.124</t>
+          <t>22196029769.0345</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>505.824</t>
+          <t>19545065716.3058</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>530.593</t>
+          <t>17249209592.6013</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>535.24</t>
+          <t>16872425975.8847</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>5894682799.9152</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>5055832922.49214</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>4106197436.49187</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>4834522206.19189</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>6734043907.74769</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>9290776577.30368</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>9083704023.45076</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>8414842325.60256</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>10003871253.5916</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>10154202306.1011</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>12576463666.7903</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>12947766203.0674</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>11324100257.6571</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>11149273624.8238</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>9623672378.60393</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>18082013.467556</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>13860531.3792213</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>12066708.5265558</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>14223993.0432986</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>17166153.2597903</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>24336201.1984143</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>23223738.7405842</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>18876301.4503446</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>19718986.7004708</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>17990202.6696558</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>20028881.5404034</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>18366225.3763597</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>13970152.3968123</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>10513188.3486126</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>12411413.2662994</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>283.294650088296</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>164.663599145164</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>146.053291689037</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>149.559536314398</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>144.005182411974</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>104.660474219366</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>92.0774148622098</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>102.710974788291</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>110.758946604041</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>129.201616480669</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>123.019908197281</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>133.659577873601</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>173.077507233041</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>205.362675168606</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>239.990077212671</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>5472.09930206733</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>4180.79652464516</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>3650.87737839016</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>4121.71461807595</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>4499.33854373248</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>4670.98558225453</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>4291.67230119554</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>3963.92282666802</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>5284.52407385223</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>6347.77590319532</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>7101.28587839497</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>7775.2620581983</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>8725.61114233787</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>8616.65947608999</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>9734.2323509872</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>-0.762759595948242</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>-0.841253111226861</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>-0.820250745855761</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>-0.837450574292253</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>-0.874752803876036</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>-0.914486808870655</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>-0.917374147854292</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>-0.905941254265202</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>-0.919166459653279</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>-0.913766399800747</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>-0.93045504231474</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>-0.929638613050203</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>-0.915844126799954</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>-0.907245395523832</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>-0.894575123071322</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>4175.97367807492</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>4262.33057798998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>4201.89573519058</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>4246.50582703679</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>4606.21276887394</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>4194.69825802974</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>4462.05534599035</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>4764.50443846394</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>5605.69135876413</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>6783.45067121095</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>7486.53790454033</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>7733.91176882276</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>9099.78319780626</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>10311.1196757243</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>9249.29863451588</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.729948331892089</t>
+          <t>29790.9999149484</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200655768488</t>
+          <t>24860.2975067939</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559175181254</t>
+          <t>19611.8744078834</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898529053504176</t>
+          <t>22047.3958865382</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.93826237298063</t>
+          <t>29116.0027302825</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271974788869</t>
+          <t>38016.2981312753</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987032739</t>
+          <t>35099.761598703</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296608032</t>
+          <t>31422.1147333927</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.88401700995807</t>
+          <t>36657.6447548245</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923167763008</t>
+          <t>36355.8979810281</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793921900143</t>
+          <t>43637.9724732488</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431998962022</t>
+          <t>43274.6196626584</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660741064353</t>
+          <t>36144.5906723814</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.6799020733193</t>
+          <t>33908.983043868</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868579003</t>
+          <t>28995.6986399636</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>24165484637.5739</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>21725974993.8131</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>15249386011.6198</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>17515820760.3498</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>27318624783.0846</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>37817435832.546</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>34956114253.0207</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>35751265824.7572</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>50687431234.109</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>53699482106.7475</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>69037342060.2193</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>87901499236.6782</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>87428102410.9743</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>82008886408.2063</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>62004823288.5999</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>5116583413.14124</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3016859277.74354</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2466696144.22682</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2887993462.42335</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3698706556.24602</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>5561044625.52525</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>3742402765.50661</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>5491059378.21158</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>6646868999.87175</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8314797457.54919</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>6437095629.85943</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9595706448.22912</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>14511569397.9297</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>6690184163.64116</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>8122515520.26577</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>19048901224.4327</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>18709115716.0695</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>12782689867.393</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>14627827297.9265</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>23619918226.8386</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>32256391207.0207</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>31213711487.5141</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>30260206446.5456</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>44040562234.2372</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>45384684649.1983</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>62600246430.3599</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>78305792788.4491</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>72916533013.0446</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>75318702244.5652</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>53882307768.3342</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>7067.62885692824</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3946.49488317816</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>3525.21979718752</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>3583.79153970813</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>3646.69770430556</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>3250.89496812991</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2900.14771220403</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2955.52470015783</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>2963.16720630486</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>3135.09997138082</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>3034.80094912262</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>3044.86225918958</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>3041.77958949249</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>3145.21431042306</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>3056.86796057919</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>6997.90722249888</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3903.96766399925</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3482.58152267232</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3546.98001542588</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3606.76143725616</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>3219.10834143844</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2874.6498958226</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2926.39498558034</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2938.19267075551</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3101.90709935345</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>3004.29548461717</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>3017.0055434524</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>3016.35811371275</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>2957.77467200876</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2836.14871444425</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-77.83</t>
+          <t>19400.2653979951</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-85.09</t>
+          <t>20026.5093451831</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-83.04</t>
+          <t>19441.5960316124</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>21316.9265954174</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-89.78</t>
+          <t>24659.1849342675</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-93.53</t>
+          <t>26084.0796568998</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-93.78</t>
+          <t>25486.7302695167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-92.92</t>
+          <t>27497.3977791202</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-93.22</t>
+          <t>33907.5962817625</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>44264.0511210012</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-94.49</t>
+          <t>49829.5222957904</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>62804.6600511222</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>79138.4897720259</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-92.69</t>
+          <t>90745.1919103551</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>79203.1585950336</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-77.21</t>
+          <t>8501167003.74831</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-84.76</t>
+          <t>6416526966.80959</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-82.66</t>
+          <t>5883568004.12134</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-83.97</t>
+          <t>6645925466.02237</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>7699679557.41166</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>9950329188.65131</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>9588232622.47295</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-90.34</t>
+          <t>8768317070.36144</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-91.22</t>
+          <t>10572559064.2115</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-90.9</t>
+          <t>12150489928.5756</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-92.6</t>
+          <t>13052528140.5689</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-92.55</t>
+          <t>14623853397.3852</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-91.04</t>
+          <t>12199598124.9391</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-90.06</t>
+          <t>10954669210.1623</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-88.28</t>
+          <t>7752565302.1163</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-74.34</t>
+          <t>15701.5489541513</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-82.85</t>
+          <t>16564.0745796391</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-80.47</t>
+          <t>16946.4131944025</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-81.38</t>
+          <t>18844.8451217108</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>21572.0694906245</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>22860.8452831074</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-89.32</t>
+          <t>22774.639078778</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-87.91</t>
+          <t>24223.1221259071</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-92.05</t>
+          <t>28878.827953222</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-88.96</t>
+          <t>38409.2714374573</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-91.15</t>
+          <t>42511.9489207111</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-91.18</t>
+          <t>51665.7075101108</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-89.33</t>
+          <t>64671.5040322085</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-88.09</t>
+          <t>74058.0755815857</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-85.51</t>
+          <t>63756.8959129889</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1508.049</t>
+          <t>17351663944.0681</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>863.948</t>
+          <t>14393933499.8822</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>793.68</t>
+          <t>12563647520.2586</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>844.536</t>
+          <t>14879906659.6111</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>901.69</t>
+          <t>19804019628.3116</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>848.879</t>
+          <t>25114530092.5692</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>799.44</t>
+          <t>24115433192.7031</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>841.339</t>
+          <t>20889900468.0133</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>860.009</t>
+          <t>26428753534.705</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>928.401</t>
+          <t>28667430499.4726</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>925.623</t>
+          <t>33306361355.5215</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>962.123</t>
+          <t>33478856737.0591</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1004.447</t>
+          <t>32882779305.9075</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1096.382</t>
+          <t>25677994590.5131</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1077.533</t>
+          <t>19681998633.5123</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1398.457</t>
+          <t>3698.7164438438</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>802.598</t>
+          <t>3462.43476554404</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>738.086</t>
+          <t>2495.18283720995</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>785.849</t>
+          <t>2472.08147370658</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>843.42</t>
+          <t>3087.11544364306</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>794.484</t>
+          <t>3223.23437379236</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>750.549</t>
+          <t>2712.09119073874</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>791.49</t>
+          <t>3274.27565321305</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>808.648</t>
+          <t>5028.76832854052</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>875.633</t>
+          <t>5854.77968354386</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>874.63</t>
+          <t>7317.57337507933</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>911.023</t>
+          <t>11138.9525410114</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>952.99</t>
+          <t>14466.9857398175</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1034.146</t>
+          <t>16687.1163287694</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1014.574</t>
+          <t>15446.2626820447</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13052.485</t>
+          <t>-8850496940.31984</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9603.687</t>
+          <t>-7977406533.07259</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8513.633</t>
+          <t>-6680079516.13729</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9771.913</t>
+          <t>-8233981193.58874</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11455.324</t>
+          <t>-12104340070.8999</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15078.685</t>
+          <t>-15164200903.9179</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14565.376</t>
+          <t>-14527200570.2302</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12802.281</t>
+          <t>-12121583397.6518</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16693.42</t>
+          <t>-15856194470.4935</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>18564.089</t>
+          <t>-16516940570.897</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21483.837</t>
+          <t>-20253833214.9526</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22196.03</t>
+          <t>-18855003339.674</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>19545.066</t>
+          <t>-20683181180.9684</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>17249.21</t>
+          <t>-14723325380.3508</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>16872.426</t>
+          <t>-11929433331.396</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6543.41082</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6330.22115</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5854.3802</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6099.46493</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6183.6647</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5735.96917</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6003.61016</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6711.77649</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>8464.65608</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9868.107</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10288.20924</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10976.83176</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13337.36511</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>14196.60338</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12450.68179</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>675.737</t>
+          <t>0.0548782722540715</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>378.248</t>
+          <t>0.0551880327512054</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>340.588</t>
+          <t>0.0445906287009296</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>354.581</t>
+          <t>0.0483580381645788</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>366.637</t>
+          <t>0.0605726996973952</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>337.861</t>
+          <t>0.0641955413602526</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>312.499</t>
+          <t>0.0491647827925677</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>331.726</t>
+          <t>0.0538649795879701</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>349.879</t>
+          <t>0.0705633395940494</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>377.85</t>
+          <t>0.0689547646175802</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>372.178</t>
+          <t>0.0755258280153297</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>381.558</t>
+          <t>0.101855351008044</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>387.688</t>
+          <t>0.113056876418437</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>411.104</t>
+          <t>0.0967459729953211</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>415.977</t>
+          <t>0.0777485062500933</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9740.1412712637</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9686.90523316738</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8888.96000180688</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9260.24573072016</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9707.83884539053</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9383.86853228874</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9974.92436313154</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11218.0306068978</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13832.6523549874</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16090.9651895715</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17349.0987159548</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18656.0812384003</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22113.8396061466</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27381.5534351554</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26920.620660565</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5894.683</t>
+          <t>10503.4413717034</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5055.833</t>
+          <t>10427.3689584264</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4106.197</t>
+          <t>9558.49779111572</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4834.522</t>
+          <t>9951.80022776958</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6734.044</t>
+          <t>10378.5343859256</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9290.777</t>
+          <t>10026.3418543322</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9083.704</t>
+          <t>10624.698944257</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8414.842</t>
+          <t>11924.556829957</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10003.871</t>
+          <t>14711.22241411</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>10154.202</t>
+          <t>17060.6380435428</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12576.464</t>
+          <t>18360.608648465</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>12947.766</t>
+          <t>19702.5215524469</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>11324.1</t>
+          <t>23307.9004151758</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11149.274</t>
+          <t>28874.9325570042</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>9623.672</t>
+          <t>28408.536187663</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>73909.4002712656</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-84.13</t>
+          <t>72364.9433489986</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-82.03</t>
+          <t>65264.9123476706</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-83.75</t>
+          <t>66189.5568281788</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>66293.7003841872</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-91.45</t>
+          <t>60799.2398683111</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-91.74</t>
+          <t>62437.8824717733</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-90.59</t>
+          <t>68342.0313112152</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-91.92</t>
+          <t>84565.0969959058</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>95992.5687797753</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>103732.684074704</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-92.96</t>
+          <t>107404.514445848</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-91.58</t>
+          <t>123173.684150599</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>140071.92969083</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-89.46</t>
+          <t>133436.289238144</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>18.082</t>
+          <t>10503.4413717034</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.861</t>
+          <t>10724.2614887281</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.067</t>
+          <t>11485.0948823644</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14.224</t>
+          <t>12182.5752783344</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>17.166</t>
+          <t>12637.43801279</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24.336</t>
+          <t>13763.6789540906</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>23.224</t>
+          <t>14880.9198597625</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18.876</t>
+          <t>15483.5148594418</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19.719</t>
+          <t>15021.8846929607</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>15520.7763738405</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20.029</t>
+          <t>16020.6517567947</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>18.366</t>
+          <t>15988.5673608761</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>16534.0276955229</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>10.513</t>
+          <t>18421.4570816226</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>12.411</t>
+          <t>19401.1993914635</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9740.1412712637</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>9950.25374335253</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10706.0225725795</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11360.6098726877</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>11810.336439702</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12876.4163248351</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>14003.4490929412</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14614.2402729657</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14167.1980987978</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14693.3330347432</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15191.3187055785</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>15166.4883979986</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>15741.3070479071</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>17527.2598775341</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>18414.3357135756</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>8231.99386829658</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8256.00944157364</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7112.09920888428</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7447.30294223042</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8621.8011740744</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8097.73837566782</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7531.80027574296</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8445.74656004296</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>11572.88701589</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>13402.5956564572</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>15321.034761535</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>18673.6362875531</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>23025.4151848242</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>23862.5148029958</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>19623.770802337</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1398456929.20883</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>802597746.602435</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>738085926.578399</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>785848808.187841</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>843420118.02106</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>794483953.195013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>750548785.577015</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>791489514.702266</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>808648330.600595</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>875633422.006662</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>874629633.53714</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>911022787.949523</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>952989545.387997</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1034146465.2671</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1014574476.11623</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1508049006.44851</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>863948044.043033</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>793680329.017021</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>844535941.672901</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>901690359.314041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>848878869.637316</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>799440136.028264</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>841338558.354347</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>860008994.730137</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>928400794.836488</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>925623438.810552</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>962123067.806969</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1004447251.86635</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1096382248.94273</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1077533399.21994</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>675736853.1242</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>378247922.663061</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>340587736.802584</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>354581269.205976</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>366637441.659819</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>337860660.32593</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>312498732.770399</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>331725630.738931</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>349879303.217409</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>377850497.821315</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>372177609.473163</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>381557810.80985</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>387687601.212287</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>411104075.344983</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>415976798.859438</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>215500</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>221300</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>227900</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>238100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>263700</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>278100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>287500</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>292700</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>299300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>308100</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>318900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>333000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>370678.084209208</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>379928.384478628</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>197867.906976744</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>203369.76744186</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>209373.023255814</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>219278.604651163</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>231283.255813953</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>244389.302325581</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>258796.744186047</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>267800</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>272900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>279300</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>288200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>299200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>313300</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>328800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>331900</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>347656915.269726</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>356524995.788177</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>369457631.879648</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>384402303.337503</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>405671073.680577</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>430517951.58852</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>450568815.623625</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>464122820.701766</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>472770403.81916</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>488325290.497368</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>502605032.235121</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>520128357.329005</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>542962614.873351</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>608295667.828685</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>598728643.090978</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>314909260.115843</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>322522139.691882</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>334261571.025526</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>348888110.389039</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>370291801.692321</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>393849815.76532</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>414010620.901615</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>426888453.077314</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>435428796.830708</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>451041569.253607</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>465532524.894422</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>483123791.169618</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>505824273.094494</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>530592586.963389</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>535239727.255658</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.215648484415565</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.199784726402223</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.194140374058004</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.207255524009581</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.219736006353015</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.239224936158196</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.24046809022498</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.239416943370824</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.146919122300035</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.295206030427211</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.313319246614321</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.281567115377296</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.309432957137098</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.300690257049695</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.379798213490054</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.328135758070723</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.340693467003098</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.389295235470385</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.434256474850671</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.475170925537629</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.463349475360647</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.455797139460949</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.455185052679172</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.432520831947049</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.424571573023134</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.417254082267022</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.435439149657932</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.410471791914278</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.420186507374171</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.41861620311448</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.456215757513712</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.459521806594679</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.416564390471611</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.358488001139748</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.305093068109356</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.297425588481156</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.303734770314071</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.305398003950004</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.420560045752916</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.280222396549656</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.269426671118657</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.282993734964772</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.280095250948624</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.279123235576134</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.201585583395466</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.187988986031401</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.174369102208575</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.170358249670412</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.166459898907562</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.162894742779448</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.162231261084635</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.161585271617819</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.162442826252358</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.117287519285537</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.204285184323656</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.219649700320424</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.193609835066314</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.212430474142803</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.207397959744257</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.269903493699397</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.32007427466936</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.331826193733228</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.38100036497172</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.430793214006936</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.478430059071846</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.47083555952887</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.463212186570251</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.46227552482524</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.475962323149365</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.448918047467116</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.444550979740482</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.460759138469995</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.442084856965206</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.449172959403727</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.467396265874686</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.49193673929924</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.493804704058197</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.448641385357869</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.402746887085502</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.358675198148706</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.366933179386495</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.37520254181193</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.375281648922402</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.406750157565099</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.346796768209227</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.335799319939094</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.345631026463691</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.345484668891991</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.343429080852016</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.262700240425917</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>38211.88115</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>39723.50636</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>37781.09976</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41560.59266</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>46884.64553</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>48649.6138</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>48930.65896</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>52493.94368</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>65341.3915</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>82023.75847</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>93916.11395</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>113315.88882</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>141769.04186</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>159357.5097</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>140559.4319</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>18735.43524</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18683.3784</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16670.597</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>17399.10317</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19000.33556</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18124.08023</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18156.49922</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20370.30339</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>26284.10943</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30463.2337</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>33681.64341</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>38376.15784</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>46333.3156</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>52737.44736</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>48032.30699</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>53950.0457319127</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>55047.3358078351</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>56404.9582185419</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>57855.4357510982</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>60009.788633893</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>61759.8030138856</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>63738.4676031019</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>65827.6917043733</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>68074.630844625</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>70460.9494699818</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>72747.8329470255</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>75066.6628894579</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>78283.2154087653</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>81384.1564773894</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>83091.2029537598</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
